--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-13).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-13).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-173</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>R$ 1.662.167,59</t>
-  </si>
-  <si>
-    <t>R$ 9.033,52
-R$ 9.198,34</t>
-  </si>
-  <si>
-    <t>(2.9%)
-(1.1%)</t>
-  </si>
-  <si>
-    <t>99.5</t>
-  </si>
-  <si>
-    <t>(7.8%)</t>
+174</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 1.667.279,52</t>
+  </si>
+  <si>
+    <t>R$ 9.012,32
+R$ 9.174,85</t>
+  </si>
+  <si>
+    <t>(3.1%)
+(1.4%)</t>
+  </si>
+  <si>
+    <t>99.4</t>
+  </si>
+  <si>
+    <t>(7.9%)</t>
   </si>
   <si>
     <t>14.1%</t>
   </si>
   <si>
-    <t>(27.9%)</t>
+    <t>(27.8%)</t>
   </si>
   <si>
     <t>2.5%</t>
@@ -950,7 +950,7 @@
     <t>30.0</t>
   </si>
   <si>
-    <t>57.3%</t>
+    <t>57.2%</t>
   </si>
   <si>
     <t>16.4%</t>
@@ -968,13 +968,13 @@
     <t>21.5</t>
   </si>
   <si>
-    <t>61.1%</t>
+    <t>61.0%</t>
   </si>
   <si>
     <t>-R$ 53.650,26</t>
   </si>
   <si>
-    <t>2.97</t>
+    <t>2.95</t>
   </si>
   <si>
     <t>3.52</t>
@@ -6646,7 +6646,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>44</v>
@@ -6682,25 +6682,59 @@
       <c t="s" r="N42" s="4">
         <v>52</v>
       </c>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
-      <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="8"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="6"/>
-      <c r="AA42" s="8"/>
-      <c r="AB42" s="8"/>
+      <c r="O42" s="5">
+        <v>5111.9300000000003</v>
+      </c>
+      <c r="P42" s="5">
+        <v>5111.9300000000003</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>-0.44778278294498275</v>
+      </c>
+      <c r="R42" s="7">
+        <v>63</v>
+      </c>
+      <c r="S42" s="6">
+        <v>-0.33684210526315794</v>
+      </c>
+      <c r="T42" s="6">
+        <v>0.39551300585101906</v>
+      </c>
+      <c r="U42" s="6">
+        <v>0.072255449507328928</v>
+      </c>
+      <c r="V42" s="6">
+        <v>0.046837887060268819</v>
+      </c>
+      <c r="W42" s="6">
+        <v>0.012547511409585028</v>
+      </c>
+      <c r="X42" s="8">
+        <v>29.893711320754718</v>
+      </c>
+      <c r="Y42" s="6">
+        <v>0.39622641509433965</v>
+      </c>
+      <c r="Z42" s="6">
+        <v>0.094339622641509441</v>
+      </c>
+      <c r="AA42" s="8">
+        <v>6.7954306451612911</v>
+      </c>
+      <c r="AB42" s="8">
+        <v>10.489795918367347</v>
+      </c>
       <c r="AC42" s="8"/>
-      <c r="AD42" s="8"/>
-      <c r="AE42" s="6"/>
+      <c r="AD42" s="8">
+        <v>23.158805660377357</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>0.49056603773584906</v>
+      </c>
       <c r="AF42" s="9"/>
-      <c r="AG42" s="5"/>
+      <c r="AG42" s="5">
+        <v>0</v>
+      </c>
       <c r="AH42" s="10">
         <v>3</v>
       </c>
@@ -15353,7 +15387,7 @@
         <v>0</v>
       </c>
       <c r="AH111" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI111" s="11"/>
       <c r="AJ111" s="13">
@@ -15706,7 +15740,7 @@
         <v>-108.7</v>
       </c>
       <c r="AH114" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI114" s="11"/>
       <c r="AJ114" s="13">

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-13).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-13).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-174</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>R$ 1.667.279,52</t>
-  </si>
-  <si>
-    <t>R$ 9.012,32
-R$ 9.174,85</t>
+175</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>R$ 1.677.468,22</t>
+  </si>
+  <si>
+    <t>R$ 9.018,65
+R$ 9.180,65</t>
   </si>
   <si>
     <t>(3.1%)
 (1.4%)</t>
   </si>
   <si>
-    <t>99.4</t>
+    <t>99.5</t>
   </si>
   <si>
     <t>(7.9%)</t>
   </si>
   <si>
-    <t>14.1%</t>
-  </si>
-  <si>
-    <t>(27.8%)</t>
+    <t>14.3%</t>
+  </si>
+  <si>
+    <t>(27.6%)</t>
   </si>
   <si>
     <t>2.5%</t>
@@ -950,10 +950,10 @@
     <t>30.0</t>
   </si>
   <si>
-    <t>57.2%</t>
-  </si>
-  <si>
-    <t>16.4%</t>
+    <t>57.0%</t>
+  </si>
+  <si>
+    <t>16.3%</t>
   </si>
   <si>
     <t>6.7</t>
@@ -962,16 +962,16 @@
     <t>8.1</t>
   </si>
   <si>
-    <t>15.0</t>
+    <t>14.9</t>
   </si>
   <si>
     <t>21.5</t>
   </si>
   <si>
-    <t>61.0%</t>
-  </si>
-  <si>
-    <t>-R$ 53.650,26</t>
+    <t>61.2%</t>
+  </si>
+  <si>
+    <t>-R$ 53.905,86</t>
   </si>
   <si>
     <t>2.95</t>
@@ -6724,7 +6724,9 @@
       <c r="AB42" s="8">
         <v>10.489795918367347</v>
       </c>
-      <c r="AC42" s="8"/>
+      <c r="AC42" s="8">
+        <v>17.379859</v>
+      </c>
       <c r="AD42" s="8">
         <v>23.158805660377357</v>
       </c>
@@ -8692,7 +8694,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>44</v>
@@ -8728,25 +8730,61 @@
       <c t="s" r="N58" s="4">
         <v>52</v>
       </c>
-      <c r="O58" s="5"/>
-      <c r="P58" s="5"/>
-      <c r="Q58" s="6"/>
-      <c r="R58" s="7"/>
-      <c r="S58" s="6"/>
-      <c r="T58" s="6"/>
-      <c r="U58" s="6"/>
-      <c r="V58" s="6"/>
-      <c r="W58" s="6"/>
-      <c r="X58" s="8"/>
-      <c r="Y58" s="6"/>
-      <c r="Z58" s="6"/>
-      <c r="AA58" s="8"/>
-      <c r="AB58" s="8"/>
-      <c r="AC58" s="8"/>
-      <c r="AD58" s="8"/>
-      <c r="AE58" s="6"/>
+      <c r="O58" s="5">
+        <v>10188.700000000001</v>
+      </c>
+      <c r="P58" s="5">
+        <v>10188.700000000001</v>
+      </c>
+      <c r="Q58" s="6">
+        <v>-0.041503761096080005</v>
+      </c>
+      <c r="R58" s="7">
+        <v>122</v>
+      </c>
+      <c r="S58" s="6">
+        <v>-0.068702290076335881</v>
+      </c>
+      <c r="T58" s="6">
+        <v>0.31554474074219474</v>
+      </c>
+      <c r="U58" s="6">
+        <v>-0.037630836122370857</v>
+      </c>
+      <c r="V58" s="6">
+        <v>0.011861523059860433</v>
+      </c>
+      <c r="W58" s="6">
+        <v>-0.00063467370714615206</v>
+      </c>
+      <c r="X58" s="8">
+        <v>24.985284042553193</v>
+      </c>
+      <c r="Y58" s="6">
+        <v>0.34042553191489361</v>
+      </c>
+      <c r="Z58" s="6">
+        <v>0.021276595744680851</v>
+      </c>
+      <c r="AA58" s="8">
+        <v>2.721311475409836</v>
+      </c>
+      <c r="AB58" s="8">
+        <v>6.6842202127659567</v>
+      </c>
+      <c r="AC58" s="8">
+        <v>9.4840409999999995</v>
+      </c>
+      <c r="AD58" s="8">
+        <v>16.371808510638299</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>0.7978723404255319</v>
+      </c>
       <c r="AF58" s="9"/>
-      <c r="AG58" s="5"/>
+      <c r="AG58" s="5">
+        <v>-255.59999999999999</v>
+      </c>
       <c r="AH58" s="10">
         <v>2</v>
       </c>
@@ -15375,7 +15413,9 @@
       <c r="AB111" s="8">
         <v>1.8015857142857143</v>
       </c>
-      <c r="AC111" s="8"/>
+      <c r="AC111" s="8">
+        <v>10.566666</v>
+      </c>
       <c r="AD111" s="8">
         <v>17.519047619047619</v>
       </c>
@@ -16877,7 +16917,7 @@
         <v>0</v>
       </c>
       <c r="AH123" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI123" s="11"/>
       <c r="AJ123" s="13">
@@ -17270,7 +17310,7 @@
         <v>0</v>
       </c>
       <c r="AH126" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI126" s="11"/>
       <c r="AJ126" s="13">
@@ -18447,7 +18487,7 @@
         <v>0</v>
       </c>
       <c r="AH135" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI135" s="11"/>
       <c r="AJ135" s="13">
@@ -20765,7 +20805,7 @@
         <v>-3077.5</v>
       </c>
       <c r="AH153" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI153" s="11"/>
       <c r="AJ153" s="13">
@@ -21977,7 +22017,7 @@
         <v>-656.5</v>
       </c>
       <c r="AH163" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI163" s="11"/>
       <c r="AJ163" s="13">
@@ -24019,7 +24059,9 @@
       <c r="AB179" s="8">
         <v>1.3242244186046512</v>
       </c>
-      <c r="AC179" s="8"/>
+      <c r="AC179" s="8">
+        <v>6.0209669999999997</v>
+      </c>
       <c r="AD179" s="8">
         <v>12.965697674418605</v>
       </c>
@@ -28100,7 +28142,7 @@
       <c r="AF212" s="9"/>
       <c r="AG212" s="5"/>
       <c r="AH212" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI212" s="11"/>
       <c r="AJ212" s="12"/>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-13).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-13).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-175</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>R$ 1.677.468,22</t>
-  </si>
-  <si>
-    <t>R$ 9.018,65
-R$ 9.180,65</t>
-  </si>
-  <si>
-    <t>(3.1%)
-(1.4%)</t>
-  </si>
-  <si>
-    <t>99.5</t>
-  </si>
-  <si>
-    <t>(7.9%)</t>
-  </si>
-  <si>
-    <t>14.3%</t>
-  </si>
-  <si>
-    <t>(27.6%)</t>
+181</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>R$ 1.726.418,26</t>
+  </si>
+  <si>
+    <t>R$ 8.991,76
+R$ 9.146,76</t>
+  </si>
+  <si>
+    <t>(3.3%)
+(1.6%)</t>
+  </si>
+  <si>
+    <t>99.1</t>
+  </si>
+  <si>
+    <t>(8.0%)</t>
+  </si>
+  <si>
+    <t>15.6%</t>
+  </si>
+  <si>
+    <t>(26.0%)</t>
   </si>
   <si>
     <t>2.5%</t>
@@ -947,34 +947,34 @@
     <t>0.5%</t>
   </si>
   <si>
-    <t>30.0</t>
-  </si>
-  <si>
-    <t>57.0%</t>
-  </si>
-  <si>
-    <t>16.3%</t>
+    <t>29.9</t>
+  </si>
+  <si>
+    <t>57.3%</t>
+  </si>
+  <si>
+    <t>16.1%</t>
   </si>
   <si>
     <t>6.7</t>
   </si>
   <si>
-    <t>8.1</t>
+    <t>8.0</t>
   </si>
   <si>
     <t>14.9</t>
   </si>
   <si>
-    <t>21.5</t>
-  </si>
-  <si>
-    <t>61.2%</t>
-  </si>
-  <si>
-    <t>-R$ 53.905,86</t>
-  </si>
-  <si>
-    <t>2.95</t>
+    <t>21.4</t>
+  </si>
+  <si>
+    <t>61.3%</t>
+  </si>
+  <si>
+    <t>-R$ 54.791,31</t>
+  </si>
+  <si>
+    <t>2.94</t>
   </si>
   <si>
     <t>3.52</t>
@@ -2066,7 +2066,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>44</v>
@@ -2102,25 +2102,61 @@
       <c t="s" r="N6" s="4">
         <v>52</v>
       </c>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="6"/>
+      <c r="O6" s="5">
+        <v>18918.279999999999</v>
+      </c>
+      <c r="P6" s="5">
+        <v>18918.279999999999</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>0.56118855871535156</v>
+      </c>
+      <c r="R6" s="7">
+        <v>194</v>
+      </c>
+      <c r="S6" s="6">
+        <v>0.48091603053435117</v>
+      </c>
+      <c r="T6" s="6">
+        <v>0.29233480527828115</v>
+      </c>
+      <c r="U6" s="6">
+        <v>-0.0088236509872990573</v>
+      </c>
+      <c r="V6" s="6">
+        <v>0.022863156692891747</v>
+      </c>
+      <c r="W6" s="6">
+        <v>0.0013834027194861269</v>
+      </c>
+      <c r="X6" s="8">
+        <v>23.20980411764706</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>0.63529411764705879</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>0.011764705882352941</v>
+      </c>
+      <c r="AA6" s="8">
+        <v>6.0056410256410251</v>
+      </c>
+      <c r="AB6" s="8">
+        <v>3.5378698224852068</v>
+      </c>
+      <c r="AC6" s="8">
+        <v>9.5763979999999993</v>
+      </c>
+      <c r="AD6" s="8">
+        <v>16.486372352941178</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>0.8411764705882353</v>
+      </c>
       <c r="AF6" s="9"/>
-      <c r="AG6" s="5"/>
+      <c r="AG6" s="5">
+        <v>-118.3</v>
+      </c>
       <c r="AH6" s="10">
         <v>5</v>
       </c>
@@ -4360,7 +4396,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>44</v>
@@ -4396,25 +4432,59 @@
       <c t="s" r="N24" s="4">
         <v>52</v>
       </c>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="7"/>
-      <c r="S24" s="6"/>
-      <c r="T24" s="6"/>
-      <c r="U24" s="6"/>
-      <c r="V24" s="6"/>
-      <c r="W24" s="6"/>
-      <c r="X24" s="8"/>
-      <c r="Y24" s="6"/>
-      <c r="Z24" s="6"/>
-      <c r="AA24" s="8"/>
-      <c r="AB24" s="8"/>
+      <c r="O24" s="5">
+        <v>8922.8799999999992</v>
+      </c>
+      <c r="P24" s="5">
+        <v>8922.8799999999992</v>
+      </c>
+      <c r="Q24" s="6">
+        <v>-0.17649903555969837</v>
+      </c>
+      <c r="R24" s="7">
+        <v>104</v>
+      </c>
+      <c r="S24" s="6">
+        <v>-0.23529411764705888</v>
+      </c>
+      <c r="T24" s="6">
+        <v>0</v>
+      </c>
+      <c r="U24" s="6">
+        <v>-0.34524727442260794</v>
+      </c>
+      <c r="V24" s="6">
+        <v>0.022095836770190794</v>
+      </c>
+      <c r="W24" s="6">
+        <v>0.0037531043788552581</v>
+      </c>
+      <c r="X24" s="8">
+        <v>33.225609756097562</v>
+      </c>
+      <c r="Y24" s="6">
+        <v>0.41463414634146339</v>
+      </c>
+      <c r="Z24" s="6">
+        <v>0.21951219512195122</v>
+      </c>
+      <c r="AA24" s="8">
+        <v>3.8980582524271843</v>
+      </c>
+      <c r="AB24" s="8">
+        <v>11.387398780487805</v>
+      </c>
       <c r="AC24" s="8"/>
-      <c r="AD24" s="8"/>
-      <c r="AE24" s="6"/>
+      <c r="AD24" s="8">
+        <v>22.332723170731708</v>
+      </c>
+      <c r="AE24" s="6">
+        <v>0.34146341463414637</v>
+      </c>
       <c r="AF24" s="9"/>
-      <c r="AG24" s="5"/>
+      <c r="AG24" s="5">
+        <v>-679.75</v>
+      </c>
       <c r="AH24" s="10">
         <v>2</v>
       </c>
@@ -5896,7 +5966,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -5932,25 +6002,61 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
-      <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="O36" s="5">
+        <v>6641.3699999999999</v>
+      </c>
+      <c r="P36" s="5">
+        <v>6641.3699999999999</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>0.1453382793462572</v>
+      </c>
+      <c r="R36" s="7">
+        <v>76</v>
+      </c>
+      <c r="S36" s="6">
+        <v>0.33333333333333326</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.30226870359579422</v>
+      </c>
+      <c r="U36" s="6">
+        <v>-0.0087288767227243769</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.070541770749107488</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.036574381490565952</v>
+      </c>
+      <c r="X36" s="8">
+        <v>25.2486984375</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>0.96875</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0.078125</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>5.5638157894736846</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>4.5942703125</v>
+      </c>
+      <c r="AC36" s="8">
+        <v>10.311717</v>
+      </c>
+      <c r="AD36" s="8">
+        <v>17.26953125</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.875</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -7817,7 +7923,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7853,25 +7959,61 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
-      <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="O51" s="5">
+        <v>1675.1400000000001</v>
+      </c>
+      <c r="P51" s="5">
+        <v>1675.1400000000001</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>-0.10010314373509244</v>
+      </c>
+      <c r="R51" s="7">
+        <v>16</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-0.27272727272727271</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.30655348209701871</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.015489451627923635</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.060928041835309282</v>
+      </c>
+      <c r="X51" s="8">
+        <v>57.218330000000002</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>0.59999999999999998</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>8.3197937500000005</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>34.67333</v>
+      </c>
+      <c r="AC51" s="8">
+        <v>45.231665999999997</v>
+      </c>
+      <c r="AD51" s="8">
+        <v>52.161670000000001</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>0.29999999999999999</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -12576,7 +12718,7 @@
         <v>0</v>
       </c>
       <c r="AH88" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI88" s="11"/>
       <c r="AJ88" s="13">
@@ -12615,7 +12757,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12649,25 +12791,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>9012.3600000000006</v>
+      </c>
+      <c r="P89" s="5">
+        <v>9012.3600000000006</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.40606485575966222</v>
+      </c>
+      <c r="R89" s="7">
+        <v>89</v>
+      </c>
+      <c r="S89" s="6">
+        <v>-0.40268456375838924</v>
+      </c>
+      <c r="T89" s="6">
+        <v>2.3580437199579243</v>
+      </c>
+      <c r="U89" s="6">
+        <v>2.0127889809106603</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.027212073197253547</v>
+      </c>
+      <c r="W89" s="6">
+        <v>0.013561930504329607</v>
+      </c>
+      <c r="X89" s="8">
+        <v>32.16050652173913</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>0.82608695652173914</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0.19565217391304349</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>7.1934862068965515</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>6.4914822222222215</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>21.310145652173912</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.41304347826086957</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>-87.400000000000006</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -16655,7 +16831,7 @@
         <v>-116.90000000000001</v>
       </c>
       <c r="AH121" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI121" s="11"/>
       <c r="AJ121" s="13">
@@ -18618,7 +18794,7 @@
         <v>-387.5</v>
       </c>
       <c r="AH136" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI136" s="11"/>
       <c r="AJ136" s="13">
@@ -20932,7 +21108,7 @@
         <v>464.80000000000001</v>
       </c>
       <c r="AH154" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI154" s="11"/>
       <c r="AJ154" s="13">
@@ -21326,7 +21502,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>44</v>
@@ -21362,25 +21538,61 @@
       <c t="s" r="N158" s="4">
         <v>52</v>
       </c>
-      <c r="O158" s="5"/>
-      <c r="P158" s="5"/>
-      <c r="Q158" s="6"/>
-      <c r="R158" s="7"/>
-      <c r="S158" s="6"/>
-      <c r="T158" s="6"/>
-      <c r="U158" s="6"/>
-      <c r="V158" s="6"/>
-      <c r="W158" s="6"/>
-      <c r="X158" s="8"/>
-      <c r="Y158" s="6"/>
-      <c r="Z158" s="6"/>
-      <c r="AA158" s="8"/>
-      <c r="AB158" s="8"/>
-      <c r="AC158" s="8"/>
-      <c r="AD158" s="8"/>
-      <c r="AE158" s="6"/>
+      <c r="O158" s="5">
+        <v>3780.0100000000002</v>
+      </c>
+      <c r="P158" s="5">
+        <v>3780.0100000000002</v>
+      </c>
+      <c r="Q158" s="6">
+        <v>-0.53528904821793655</v>
+      </c>
+      <c r="R158" s="7">
+        <v>41</v>
+      </c>
+      <c r="S158" s="6">
+        <v>-0.5</v>
+      </c>
+      <c r="T158" s="6">
+        <v>0.27251385578345028</v>
+      </c>
+      <c r="U158" s="6">
+        <v>-0.019427170827590403</v>
+      </c>
+      <c r="V158" s="6">
+        <v>0.033517900746294321</v>
+      </c>
+      <c r="W158" s="6">
+        <v>-0.00031005208980928621</v>
+      </c>
+      <c r="X158" s="8">
+        <v>30.811615151515152</v>
+      </c>
+      <c r="Y158" s="6">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="Z158" s="6">
+        <v>0.090909090909090912</v>
+      </c>
+      <c r="AA158" s="8">
+        <v>5.4788609756097557</v>
+      </c>
+      <c r="AB158" s="8">
+        <v>7.1732333333333331</v>
+      </c>
+      <c r="AC158" s="8">
+        <v>12.253534999999999</v>
+      </c>
+      <c r="AD158" s="8">
+        <v>19.207575757575757</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0.48484848484848486</v>
+      </c>
       <c r="AF158" s="9"/>
-      <c r="AG158" s="5"/>
+      <c r="AG158" s="5">
+        <v>0</v>
+      </c>
       <c r="AH158" s="10">
         <v>2</v>
       </c>
